--- a/ASN/Snapone_220RT_出貨報表_4116684783 shipping list.xlsx
+++ b/ASN/Snapone_220RT_出貨報表_4116684783 shipping list.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30413"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liteon-my.sharepoint.com/personal/ashley_yh_chen_liteon_com/Documents/SNAP/11. 出貨文件/2026/20260820-AU/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Stanley\U-Media\光寶LITEON\ASN\ASN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D32D634C-E76F-4A3D-BEAD-C6C39A3D3AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999ECC34-5D6C-42D3-AEDF-20DEACD6712F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,28 +16,17 @@
     <sheet name="Data" sheetId="1" r:id="rId1"/>
     <sheet name="欄位說明" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2212" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2228" uniqueCount="557">
   <si>
     <t>COMPLETE_TIME</t>
   </si>
@@ -1693,6 +1682,26 @@
   </si>
   <si>
     <t>PO No.CS出貨通知</t>
+  </si>
+  <si>
+    <t>ModelName</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>產品名稱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>v</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SA-AN-220-RT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SA-AN-520-RT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1700,15 +1709,26 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
+    <numFmt numFmtId="176" formatCode="yyyy/mm/dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="9"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="細明體"/>
       <family val="3"/>
       <charset val="136"/>
@@ -1739,11 +1759,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2079,28 +2101,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S121"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="4.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="19.85546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2159,7 +2181,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>19</v>
       </c>
@@ -2218,7 +2240,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:19">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
@@ -2277,7 +2299,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:19">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
@@ -2336,7 +2358,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
@@ -2395,7 +2417,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:19">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -2454,7 +2476,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:19">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
@@ -2513,7 +2535,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:19">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -2572,7 +2594,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
@@ -2631,7 +2653,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -2690,7 +2712,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -2749,7 +2771,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -2808,7 +2830,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
@@ -2867,7 +2889,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
@@ -2926,7 +2948,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:19">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
@@ -2985,7 +3007,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -3044,7 +3066,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
@@ -3103,7 +3125,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
@@ -3162,7 +3184,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
@@ -3221,7 +3243,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -3280,7 +3302,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -3339,7 +3361,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>19</v>
       </c>
@@ -3398,7 +3420,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -3457,7 +3479,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -3516,7 +3538,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -3575,7 +3597,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -3634,7 +3656,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -3693,7 +3715,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -3752,7 +3774,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -3811,7 +3833,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>19</v>
       </c>
@@ -3870,7 +3892,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>19</v>
       </c>
@@ -3929,7 +3951,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>19</v>
       </c>
@@ -3988,7 +4010,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>19</v>
       </c>
@@ -4047,7 +4069,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>19</v>
       </c>
@@ -4106,7 +4128,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>19</v>
       </c>
@@ -4165,7 +4187,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>19</v>
       </c>
@@ -4224,7 +4246,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>19</v>
       </c>
@@ -4283,7 +4305,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>19</v>
       </c>
@@ -4342,7 +4364,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>19</v>
       </c>
@@ -4401,7 +4423,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>19</v>
       </c>
@@ -4460,7 +4482,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>19</v>
       </c>
@@ -4519,7 +4541,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>19</v>
       </c>
@@ -4578,7 +4600,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>19</v>
       </c>
@@ -4637,7 +4659,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>19</v>
       </c>
@@ -4696,7 +4718,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>19</v>
       </c>
@@ -4755,7 +4777,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
@@ -4814,7 +4836,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>19</v>
       </c>
@@ -4873,7 +4895,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>19</v>
       </c>
@@ -4932,7 +4954,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>19</v>
       </c>
@@ -4991,7 +5013,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>19</v>
       </c>
@@ -5050,7 +5072,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>19</v>
       </c>
@@ -5109,7 +5131,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>19</v>
       </c>
@@ -5168,7 +5190,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>19</v>
       </c>
@@ -5227,7 +5249,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="54" spans="1:19">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>19</v>
       </c>
@@ -5286,7 +5308,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>19</v>
       </c>
@@ -5345,7 +5367,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:19">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>19</v>
       </c>
@@ -5404,7 +5426,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="57" spans="1:19">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>19</v>
       </c>
@@ -5463,7 +5485,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>19</v>
       </c>
@@ -5522,7 +5544,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>19</v>
       </c>
@@ -5581,7 +5603,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="60" spans="1:19">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>19</v>
       </c>
@@ -5640,7 +5662,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>19</v>
       </c>
@@ -5699,7 +5721,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>19</v>
       </c>
@@ -5758,7 +5780,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>19</v>
       </c>
@@ -5817,7 +5839,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>19</v>
       </c>
@@ -5876,7 +5898,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="65" spans="1:19">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>19</v>
       </c>
@@ -5935,7 +5957,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>19</v>
       </c>
@@ -5994,7 +6016,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="67" spans="1:19">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>19</v>
       </c>
@@ -6053,7 +6075,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>19</v>
       </c>
@@ -6112,7 +6134,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>19</v>
       </c>
@@ -6171,7 +6193,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>19</v>
       </c>
@@ -6230,7 +6252,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>19</v>
       </c>
@@ -6289,7 +6311,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>19</v>
       </c>
@@ -6348,7 +6370,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>19</v>
       </c>
@@ -6407,7 +6429,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>19</v>
       </c>
@@ -6466,7 +6488,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>19</v>
       </c>
@@ -6525,7 +6547,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>19</v>
       </c>
@@ -6584,7 +6606,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>19</v>
       </c>
@@ -6643,7 +6665,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>19</v>
       </c>
@@ -6702,7 +6724,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="79" spans="1:19">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>19</v>
       </c>
@@ -6761,7 +6783,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>19</v>
       </c>
@@ -6820,7 +6842,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="81" spans="1:19">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>19</v>
       </c>
@@ -6879,7 +6901,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="82" spans="1:19">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>19</v>
       </c>
@@ -6938,7 +6960,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="83" spans="1:19">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>19</v>
       </c>
@@ -6997,7 +7019,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="84" spans="1:19">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>19</v>
       </c>
@@ -7056,7 +7078,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="85" spans="1:19">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>19</v>
       </c>
@@ -7115,7 +7137,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="86" spans="1:19">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>19</v>
       </c>
@@ -7174,7 +7196,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="87" spans="1:19">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>19</v>
       </c>
@@ -7233,7 +7255,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="88" spans="1:19">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>19</v>
       </c>
@@ -7292,7 +7314,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="89" spans="1:19">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>19</v>
       </c>
@@ -7351,7 +7373,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="90" spans="1:19">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>19</v>
       </c>
@@ -7410,7 +7432,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="91" spans="1:19">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>19</v>
       </c>
@@ -7469,7 +7491,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="92" spans="1:19">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>19</v>
       </c>
@@ -7528,7 +7550,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="93" spans="1:19">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>19</v>
       </c>
@@ -7587,7 +7609,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="94" spans="1:19">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>19</v>
       </c>
@@ -7646,7 +7668,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="95" spans="1:19">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>19</v>
       </c>
@@ -7705,7 +7727,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="96" spans="1:19">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>19</v>
       </c>
@@ -7764,7 +7786,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="97" spans="1:19">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>19</v>
       </c>
@@ -7823,7 +7845,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="98" spans="1:19">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>19</v>
       </c>
@@ -7882,7 +7904,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="99" spans="1:19">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>19</v>
       </c>
@@ -7941,7 +7963,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="100" spans="1:19">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>19</v>
       </c>
@@ -8000,7 +8022,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="101" spans="1:19">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>19</v>
       </c>
@@ -8059,7 +8081,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="102" spans="1:19">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>19</v>
       </c>
@@ -8118,7 +8140,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="103" spans="1:19">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>19</v>
       </c>
@@ -8177,7 +8199,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="104" spans="1:19">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>19</v>
       </c>
@@ -8236,7 +8258,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="105" spans="1:19">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>19</v>
       </c>
@@ -8295,7 +8317,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="106" spans="1:19">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>19</v>
       </c>
@@ -8354,7 +8376,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="107" spans="1:19">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>19</v>
       </c>
@@ -8413,7 +8435,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="108" spans="1:19">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>19</v>
       </c>
@@ -8472,7 +8494,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="109" spans="1:19">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>19</v>
       </c>
@@ -8531,7 +8553,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="110" spans="1:19">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>19</v>
       </c>
@@ -8590,7 +8612,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="111" spans="1:19">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>19</v>
       </c>
@@ -8649,7 +8671,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="112" spans="1:19">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>19</v>
       </c>
@@ -8708,7 +8730,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="113" spans="1:19">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>19</v>
       </c>
@@ -8767,7 +8789,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="114" spans="1:19">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>19</v>
       </c>
@@ -8826,7 +8848,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="115" spans="1:19">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>19</v>
       </c>
@@ -8885,7 +8907,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="116" spans="1:19">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>19</v>
       </c>
@@ -8944,7 +8966,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="117" spans="1:19">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>19</v>
       </c>
@@ -9003,7 +9025,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="118" spans="1:19">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>19</v>
       </c>
@@ -9062,7 +9084,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="119" spans="1:19">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>19</v>
       </c>
@@ -9121,7 +9143,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="120" spans="1:19">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>19</v>
       </c>
@@ -9180,7 +9202,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="121" spans="1:19">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>19</v>
       </c>
@@ -9247,124 +9269,177 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D54C13F-B389-44A4-B55C-A2E7A6A73CB0}">
-  <dimension ref="A1:S2"/>
-  <sheetFormatPr defaultColWidth="16.140625" defaultRowHeight="15"/>
+  <dimension ref="A1:T4"/>
+  <sheetFormatPr defaultColWidth="16.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="21.140625" customWidth="1"/>
-    <col min="17" max="17" width="24.7109375" customWidth="1"/>
-    <col min="18" max="18" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" customWidth="1"/>
+    <col min="18" max="18" width="24.6640625" customWidth="1"/>
+    <col min="19" max="19" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19">
-      <c r="A2" t="s">
+    <row r="2" spans="1:20" ht="15" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="B2" t="s">
         <v>539</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>540</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>541</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>542</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>543</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>544</v>
-      </c>
-      <c r="G2" t="s">
-        <v>542</v>
       </c>
       <c r="H2" t="s">
         <v>542</v>
       </c>
       <c r="I2" t="s">
+        <v>542</v>
+      </c>
+      <c r="J2" t="s">
         <v>545</v>
       </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
         <v>546</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>547</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>548</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>549</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>550</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>551</v>
       </c>
     </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>554</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>